--- a/results/ate_iptw_cox_time_interaction_IPTW_Cox_TimeInteraction_retention.xlsx
+++ b/results/ate_iptw_cox_time_interaction_IPTW_Cox_TimeInteraction_retention.xlsx
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.227</v>
+        <v>-0.008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.022</v>
+        <v>-0.001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.205</v>
+        <v>0.007</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -636,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.143</v>
+        <v>-0.066</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.042</v>
+        <v>-0.057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.101</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.001</v>
+        <v>-0.027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008</v>
+        <v>0.027</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -690,7 +690,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.024</v>
+        <v>0.041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.025</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>-0.018</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -744,7 +744,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,16 +753,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D12" t="n">
-        <v>0.042</v>
+        <v>-0.042</v>
       </c>
       <c r="E12" t="n">
-        <v>0.065</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -771,7 +771,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>-0.008</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.018</v>
+        <v>0.026</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.128</v>
+        <v>-0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.019</v>
+        <v>-0.013</v>
       </c>
       <c r="E14" t="n">
-        <v>0.109</v>
+        <v>0.028</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -852,7 +852,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.013</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -879,7 +879,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.046</v>
+        <v>-0.401</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002</v>
+        <v>-0.038</v>
       </c>
       <c r="E17" t="n">
-        <v>0.044</v>
+        <v>0.363</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.392</v>
+        <v>-0.014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>-0.003</v>
       </c>
       <c r="E18" t="n">
-        <v>0.362</v>
+        <v>0.011</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.042</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.101</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -960,7 +960,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.197</v>
+        <v>-0.019</v>
       </c>
       <c r="D20" t="n">
-        <v>0.065</v>
+        <v>-0.023</v>
       </c>
       <c r="E20" t="n">
-        <v>0.132</v>
+        <v>-0.004</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -987,7 +987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.042</v>
+        <v>-0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1041,7 +1041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.023</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E23" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.401</v>
+        <v>0.022</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.038</v>
+        <v>0.015</v>
       </c>
       <c r="E24" t="n">
-        <v>0.363</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.041</v>
+        <v>-0.024</v>
       </c>
       <c r="D25" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003000000000000003</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1149,7 +1149,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1158,16 +1158,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.066</v>
+        <v>0.197</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.057</v>
+        <v>0.065</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1176,7 +1176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.041</v>
+        <v>0.046</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="E28" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.022</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.015</v>
-      </c>
       <c r="E29" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1230,7 +1230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.027</v>
+        <v>-0.013</v>
       </c>
       <c r="E30" t="n">
-        <v>0.027</v>
+        <v>-0.008</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1257,7 +1257,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.019</v>
+        <v>0.107</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.023</v>
+        <v>0.042</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.004</v>
+        <v>0.065</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1284,7 +1284,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.014</v>
+        <v>-0.128</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.003</v>
+        <v>0.019</v>
       </c>
       <c r="E32" t="n">
-        <v>0.011</v>
+        <v>0.109</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1311,7 +1311,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>0.392</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004</v>
+        <v>0.03</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.004</v>
+        <v>0.362</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -1397,10 +1397,10 @@
         <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1325095691671195</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120529</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
         <v>1.124267686541995</v>
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981337</v>
+        <v>0.4771933030981192</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271335e-08</v>
+        <v>1.938181768269377e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516169</v>
+        <v>-0.02542074333516158</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7997554080121694</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -1744,7 +1744,7 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442913</v>
+        <v>0.2335027157442912</v>
       </c>
       <c r="D4" t="n">
         <v>0.3364439424069158</v>
@@ -1763,7 +1763,7 @@
         <v>0.1734026513921179</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054353e-06</v>
+        <v>2.563995828054338e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387288</v>
+        <v>0.03527526670387286</v>
       </c>
       <c r="C6" t="n">
         <v>0.1916882946919541</v>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307714</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
         <v>0.1901447102133383</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125522</v>
+        <v>0.1446466431125519</v>
       </c>
     </row>
     <row r="8">
@@ -1808,10 +1808,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982441</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432465</v>
+        <v>0.5954095400432462</v>
       </c>
     </row>
     <row r="9">
@@ -1824,10 +1824,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409134</v>
+        <v>0.1695280942409135</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342607e-07</v>
+        <v>2.539495077342677e-07</v>
       </c>
     </row>
     <row r="10">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617097</v>
+        <v>-0.04456520772617082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171631</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.864113709151783</v>
+        <v>0.8641137091517835</v>
       </c>
     </row>
     <row r="11">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798147</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465059</v>
+        <v>0.278788138546506</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877618</v>
+        <v>0.3261132423877624</v>
       </c>
     </row>
     <row r="12">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118135</v>
+        <v>0.08100487957118152</v>
       </c>
       <c r="C12" t="n">
         <v>0.259642977209717</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424693</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461744</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743773</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123741</v>
       </c>
     </row>
     <row r="14">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307938</v>
+        <v>-0.05296103812307937</v>
       </c>
       <c r="C14" t="n">
         <v>0.2610089865588713</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.118132272653416</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577178</v>
+        <v>0.2572294350577181</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984078</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379422</v>
+        <v>-0.004000986240379116</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311191</v>
+        <v>0.2383903410311188</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655135</v>
+        <v>0.9866094604655145</v>
       </c>
     </row>
     <row r="17">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395305</v>
+        <v>0.1057185310395307</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421747</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567299</v>
+        <v>0.6776529122567304</v>
       </c>
     </row>
     <row r="18">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733255</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
         <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546262</v>
+        <v>0.6013412201546269</v>
       </c>
     </row>
     <row r="19">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223242</v>
+        <v>-0.02557154094223222</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538109</v>
+        <v>0.2527597901538111</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966674</v>
+        <v>0.9194160355966681</v>
       </c>
     </row>
     <row r="20">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376422</v>
+        <v>-0.07344622569376401</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541008</v>
+        <v>0.2674578609541015</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222774</v>
+        <v>0.7836169672222785</v>
       </c>
     </row>
     <row r="21">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305063</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450721</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719842</v>
       </c>
     </row>
     <row r="22">
@@ -2032,10 +2032,10 @@
         <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.26967484549659</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806356</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445709</v>
+        <v>0.2870672180445712</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171774</v>
+        <v>0.0810583897517182</v>
       </c>
     </row>
     <row r="24">
@@ -2067,7 +2067,7 @@
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.713396260923912e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421805</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103797e-07</v>
+        <v>4.401383208103902e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441739</v>
+        <v>0.237316144844174</v>
       </c>
       <c r="C26" t="n">
         <v>0.1503781926377479</v>
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998647</v>
+        <v>-0.04350476117998651</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386413</v>
+        <v>0.1611879340386412</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400217</v>
+        <v>0.7872365295400213</v>
       </c>
     </row>
     <row r="28">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975731</v>
+        <v>-0.07514354096975727</v>
       </c>
       <c r="C28" t="n">
         <v>0.1613683918223564</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120147</v>
+        <v>0.6414556246120149</v>
       </c>
     </row>
     <row r="29">
@@ -2141,93 +2141,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09749293462742091</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290166</v>
+        <v>0.1543265796290164</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510013</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192863</v>
+        <v>0.006335499136474496</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00713578100345852</v>
+        <v>0.006871422968197218</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418278</v>
+        <v>0.356524995766646</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962211</v>
+        <v>-0.002418133412192862</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454689</v>
+        <v>0.007135781003458521</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341392</v>
+        <v>0.734704360341828</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.00412965602647542</v>
+        <v>0.2280638724458786</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033175</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D32" t="n">
-        <v>0.852577067296128</v>
+        <v>0.04668969945129909</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458786</v>
+        <v>-0.005012017390962165</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.00830487699245463</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129909</v>
+        <v>0.54617418353414</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474501</v>
+        <v>-0.004129656026475389</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197203</v>
+        <v>0.02222260881033175</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666446</v>
+        <v>0.8525770672961291</v>
       </c>
     </row>
   </sheetData>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.900193688823673</v>
+        <v>0.9001936888236722</v>
       </c>
       <c r="D3" t="n">
         <v>0.8548025202490657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04539116857460734</v>
+        <v>0.04539116857460657</v>
       </c>
     </row>
     <row r="4">
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8720187983946986</v>
+        <v>0.872018798394698</v>
       </c>
       <c r="D4" t="n">
         <v>0.8250397507431066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.046979047651592</v>
+        <v>0.04697904765159133</v>
       </c>
     </row>
     <row r="5">
@@ -2341,10 +2341,10 @@
         <v>0.8436439126637496</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7967552731684091</v>
+        <v>0.7967552731684119</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0468886394953405</v>
+        <v>0.04688863949533773</v>
       </c>
     </row>
   </sheetData>
@@ -2388,7 +2388,7 @@
         <v>294.5429333691334</v>
       </c>
       <c r="B2" t="n">
-        <v>5.09000578308233e-66</v>
+        <v>5.090005783082184e-66</v>
       </c>
       <c r="C2" t="n">
         <v>216.8995869671256</v>
@@ -2397,22 +2397,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>490.0385614716633</v>
+        <v>490.0385614716636</v>
       </c>
       <c r="B3" t="n">
-        <v>1.397724509693327e-108</v>
+        <v>1.397724509693088e-108</v>
       </c>
       <c r="C3" t="n">
-        <v>358.2851542130625</v>
+        <v>358.2851542130627</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>750.969941616192</v>
+        <v>750.9699416161922</v>
       </c>
       <c r="B4" t="n">
-        <v>2.468888780414512e-165</v>
+        <v>2.468888780414373e-165</v>
       </c>
       <c r="C4" t="n">
         <v>546.8142738096298</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.142274341703341</v>
+        <v>1.142274341703333</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2851722601515715</v>
+        <v>0.2851722601515733</v>
       </c>
       <c r="C5" t="n">
-        <v>1.810094443007944</v>
+        <v>1.810094443007935</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
@@ -2436,28 +2436,28 @@
         <v>1.332870369642652</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2482952173346544</v>
+        <v>0.2482952173346543</v>
       </c>
       <c r="C6" t="n">
-        <v>2.009871622313523</v>
+        <v>2.009871622313524</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.255849807558129</v>
+        <v>1.255849807558127</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2624381298008734</v>
+        <v>0.2624381298008739</v>
       </c>
       <c r="C7" t="n">
-        <v>1.929950749633189</v>
+        <v>1.929950749633187</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.566766284228127</v>
+        <v>1.566766284228126</v>
       </c>
       <c r="B8" t="n">
         <v>0.2106772497604381</v>
@@ -2469,349 +2469,349 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.574957324834588</v>
+        <v>6.574957324834555</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0103423483000428</v>
+        <v>0.01034234830004299</v>
       </c>
       <c r="C9" t="n">
-        <v>6.595292393273082</v>
+        <v>6.595292393273056</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.7436106862930218</v>
+        <v>0.7436106862930115</v>
       </c>
       <c r="B10" t="n">
-        <v>0.388506695839651</v>
+        <v>0.3885066958396542</v>
       </c>
       <c r="C10" t="n">
-        <v>1.363988631463092</v>
+        <v>1.36398863146308</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.108437182271659</v>
+        <v>1.108437182271647</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2924219228644659</v>
+        <v>0.2924219228644685</v>
       </c>
       <c r="C11" t="n">
-        <v>1.773876620730248</v>
+        <v>1.773876620730235</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.3303658657160227</v>
+        <v>0.330365865716019</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5654437324694603</v>
+        <v>0.5654437324694624</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8225446266866093</v>
+        <v>0.822544626686604</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2.557369788172989</v>
+        <v>2.557369788172969</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1097810910580783</v>
+        <v>0.1097810910580799</v>
       </c>
       <c r="C13" t="n">
-        <v>3.18729851218336</v>
+        <v>3.187298512183339</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.9003581826524448</v>
+        <v>0.9003581826524371</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3426856873782355</v>
+        <v>0.3426856873782375</v>
       </c>
       <c r="C14" t="n">
-        <v>1.545042157420832</v>
+        <v>1.545042157420824</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.432237332778629</v>
+        <v>1.432237332778615</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2313996514054113</v>
+        <v>0.2313996514054136</v>
       </c>
       <c r="C15" t="n">
-        <v>2.111541403804376</v>
+        <v>2.111541403804362</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.063235339674793</v>
+        <v>2.063235339674784</v>
       </c>
       <c r="B16" t="n">
-        <v>0.15088950551313</v>
+        <v>0.1508895055131309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.728435626137831</v>
+        <v>2.728435626137824</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1958606284066945</v>
+        <v>0.1958606284066902</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6580829806410309</v>
+        <v>0.6580829806410344</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6036585835541424</v>
+        <v>0.6036585835541346</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.617202257648798</v>
+        <v>5.617202257648764</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01778501760915514</v>
+        <v>0.01778501760915551</v>
       </c>
       <c r="C18" t="n">
-        <v>5.813193786944924</v>
+        <v>5.813193786944893</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.417029330831444</v>
+        <v>1.417029330831436</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2338929801225852</v>
+        <v>0.2338929801225864</v>
       </c>
       <c r="C19" t="n">
-        <v>2.096079532445899</v>
+        <v>2.096079532445892</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3.645392438578122</v>
+        <v>3.645392438578116</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05622455201226741</v>
+        <v>0.05622455201226762</v>
       </c>
       <c r="C20" t="n">
-        <v>4.152655928876213</v>
+        <v>4.152655928876207</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.290214552259818</v>
+        <v>0.2902145522598145</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5900830729575427</v>
+        <v>0.5900830729575449</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7610100209091413</v>
+        <v>0.7610100209091359</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.463998911237554</v>
+        <v>3.463998911237537</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06271846142450611</v>
+        <v>0.06271846142450672</v>
       </c>
       <c r="C22" t="n">
-        <v>3.994966021304719</v>
+        <v>3.994966021304705</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.007612562333025163</v>
+        <v>0.007612562333023579</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9304727973639287</v>
+        <v>0.930472797363936</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1039641215850145</v>
+        <v>0.1039641215850033</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.376123154591636</v>
+        <v>3.376123154591638</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06614747908136633</v>
+        <v>0.06614747908136591</v>
       </c>
       <c r="C24" t="n">
-        <v>3.918170014164392</v>
+        <v>3.918170014164401</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4093029449366719</v>
+        <v>0.409302944936669</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5223235151329908</v>
+        <v>0.5223235151329922</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9369844392298811</v>
+        <v>0.9369844392298771</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.193729552093395</v>
+        <v>1.193729552093392</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2745785502907854</v>
+        <v>0.2745785502907858</v>
       </c>
       <c r="C26" t="n">
-        <v>1.864709166408129</v>
+        <v>1.864709166408127</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.03913855261814916</v>
+        <v>0.03913855261814785</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8431744274775961</v>
+        <v>0.8431744274775987</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2460969825501809</v>
+        <v>0.2460969825501764</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1260727750053983</v>
+        <v>0.1260727750054008</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7225391866368639</v>
+        <v>0.7225391866368611</v>
       </c>
       <c r="C28" t="n">
-        <v>0.468852261137596</v>
+        <v>0.4688522611376015</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.2420351704626618</v>
+        <v>0.242035170462663</v>
       </c>
       <c r="B29" t="n">
-        <v>0.6227400561675778</v>
+        <v>0.622740056167577</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6832980150045652</v>
+        <v>0.683298015004567</v>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.78340523959319</v>
+        <v>0.7834052395931936</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3761017155639748</v>
+        <v>0.3761017155639738</v>
       </c>
       <c r="C30" t="n">
-        <v>1.41080520773277</v>
+        <v>1.410805207732774</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.446774758348337</v>
+        <v>2.446774758348324</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1177666210589438</v>
+        <v>0.1177666210589458</v>
       </c>
       <c r="C31" t="n">
-        <v>3.085997405095337</v>
+        <v>3.085997405095313</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.9507764331418014</v>
+        <v>0.9507764331417977</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3295217416659624</v>
+        <v>0.3295217416659633</v>
       </c>
       <c r="C32" t="n">
-        <v>1.601554438276596</v>
+        <v>1.601554438276592</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.200490831679793</v>
+        <v>1.200490831679786</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2732235989266673</v>
+        <v>0.2732235989266686</v>
       </c>
       <c r="C33" t="n">
-        <v>1.871845997115456</v>
+        <v>1.871845997115449</v>
       </c>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.2236537360085931</v>
+        <v>0.2236537360085907</v>
       </c>
       <c r="B34" t="n">
-        <v>0.6362699465437938</v>
+        <v>0.6362699465437953</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6522891156774261</v>
+        <v>0.6522891156774225</v>
       </c>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.15467288874499</v>
+        <v>1.154672888744988</v>
       </c>
       <c r="B35" t="n">
-        <v>0.2825730825236617</v>
+        <v>0.282573082523662</v>
       </c>
       <c r="C35" t="n">
-        <v>1.8233040515764</v>
+        <v>1.823304051576398</v>
       </c>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.23543935722114</v>
+        <v>1.235439357221134</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2663518146526981</v>
+        <v>0.2663518146526994</v>
       </c>
       <c r="C36" t="n">
-        <v>1.908594984885502</v>
+        <v>1.908594984885495</v>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7306509873324896</v>
+        <v>0.7306509873324871</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3926722595246461</v>
+        <v>0.3926722595246471</v>
       </c>
       <c r="C37" t="n">
-        <v>1.348602413001826</v>
+        <v>1.348602413001822</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2821,13 +2821,13 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.1638558207844899</v>
+        <v>0.1638558207844853</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6856310839467112</v>
+        <v>0.6856310839467153</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5444955775617865</v>
+        <v>0.5444955775617778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2837,13 +2837,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.3127434814315061</v>
+        <v>0.3127434814315037</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5760015348351368</v>
+        <v>0.5760015348351384</v>
       </c>
       <c r="C39" t="n">
-        <v>0.795855438955729</v>
+        <v>0.7958554389557251</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.4413135992851873</v>
+        <v>0.4413135992851767</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5064891174464708</v>
+        <v>0.5064891174464761</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9813968236391855</v>
+        <v>0.9813968236391706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/results/ate_iptw_cox_time_interaction_IPTW_Cox_TimeInteraction_retention.xlsx
+++ b/results/ate_iptw_cox_time_interaction_IPTW_Cox_TimeInteraction_retention.xlsx
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="E7" t="n">
         <v>-0.008</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.007</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -636,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.066</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.057</v>
+        <v>-0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.004</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.054</v>
+        <v>-0.401</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.027</v>
+        <v>-0.038</v>
       </c>
       <c r="E9" t="n">
-        <v>0.027</v>
+        <v>0.363</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -690,7 +690,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.041</v>
+        <v>0.197</v>
       </c>
       <c r="D10" t="n">
-        <v>0.038</v>
+        <v>0.065</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.132</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.025</v>
+        <v>-0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.018</v>
+        <v>0.008</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -744,7 +744,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.074</v>
+        <v>0.034</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.042</v>
+        <v>-0.008</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -771,7 +771,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.034</v>
+        <v>0.023</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.041</v>
+        <v>-0.074</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.013</v>
+        <v>-0.042</v>
       </c>
       <c r="E14" t="n">
-        <v>0.028</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>0.107</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.065</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -852,7 +852,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.023</v>
+        <v>-0.019</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.023</v>
       </c>
       <c r="E16" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -879,7 +879,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.401</v>
+        <v>0.032</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.038</v>
+        <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>0.363</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.014</v>
+        <v>0.227</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.003</v>
+        <v>0.022</v>
       </c>
       <c r="E18" t="n">
-        <v>0.011</v>
+        <v>0.205</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>0.392</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.042</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>0.101</v>
+        <v>0.362</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -960,7 +960,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>-0.041</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.023</v>
+        <v>-0.013</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.004</v>
+        <v>0.028</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -987,7 +987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001</v>
+        <v>0.031</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008</v>
+        <v>0.046</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1014,7 +1014,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>0.041</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>0.038</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1041,7 +1041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
+        <v>-0.066</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.004</v>
+        <v>-0.057</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.004</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.022</v>
+        <v>-0.014</v>
       </c>
       <c r="D24" t="n">
-        <v>0.015</v>
+        <v>-0.003</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.024</v>
+        <v>0.007</v>
       </c>
       <c r="D25" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.002999999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.077</v>
+        <v>0.022</v>
       </c>
       <c r="D26" t="n">
-        <v>0.031</v>
+        <v>0.015</v>
       </c>
       <c r="E26" t="n">
-        <v>0.046</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1149,7 +1149,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.197</v>
+        <v>-0.113</v>
       </c>
       <c r="D27" t="n">
-        <v>0.065</v>
+        <v>-0.05</v>
       </c>
       <c r="E27" t="n">
-        <v>0.132</v>
+        <v>0.063</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.002</v>
+        <v>0.027</v>
       </c>
       <c r="E28" t="n">
-        <v>0.044</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.227</v>
+        <v>-0.008</v>
       </c>
       <c r="D29" t="n">
-        <v>0.022</v>
+        <v>-0.001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.205</v>
+        <v>0.007</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1230,7 +1230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1239,16 +1239,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.005</v>
+        <v>-0.128</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.013</v>
+        <v>0.019</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.008</v>
+        <v>0.109</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1257,7 +1257,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.107</v>
+        <v>-0.143</v>
       </c>
       <c r="D31" t="n">
-        <v>0.042</v>
+        <v>-0.042</v>
       </c>
       <c r="E31" t="n">
-        <v>0.065</v>
+        <v>0.101</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1284,7 +1284,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.128</v>
+        <v>-0.054</v>
       </c>
       <c r="D32" t="n">
-        <v>0.019</v>
+        <v>-0.027</v>
       </c>
       <c r="E32" t="n">
-        <v>0.109</v>
+        <v>0.027</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1311,7 +1311,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.392</v>
+        <v>0.046</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03</v>
+        <v>-0.002</v>
       </c>
       <c r="E33" t="n">
-        <v>0.362</v>
+        <v>0.044</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.68060017980294</v>
+        <v>-2.680600179802941</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981192</v>
+        <v>0.477193303098152</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768269377e-08</v>
+        <v>1.938181768273688e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442912</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069158</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8155080917228589</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921179</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054338e-06</v>
+        <v>2.563995828054396e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387286</v>
+        <v>0.03527526670387304</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919541</v>
+        <v>0.1916882946919543</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713553</v>
+        <v>0.8539945454713549</v>
       </c>
     </row>
     <row r="7">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2773648159307717</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133383</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125519</v>
+        <v>0.1446466431125524</v>
       </c>
     </row>
     <row r="8">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1036811851537242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982441</v>
+        <v>0.1952515666982446</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432462</v>
+        <v>0.5954095400432466</v>
       </c>
     </row>
     <row r="9">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8738774480300986</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409135</v>
+        <v>0.1695280942409138</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342677e-07</v>
+        <v>2.539495077342793e-07</v>
       </c>
     </row>
     <row r="10">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617082</v>
+        <v>-0.04456520772617081</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.2604021031716311</v>
       </c>
       <c r="D10" t="n">
         <v>0.8641137091517835</v>
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798147</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.278788138546506</v>
+        <v>0.2787881385465062</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877624</v>
+        <v>0.3261132423877625</v>
       </c>
     </row>
     <row r="12">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118152</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.259642977209717</v>
+        <v>0.2596429772097175</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424689</v>
+        <v>0.75505143914247</v>
       </c>
     </row>
     <row r="13">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.03917827337461743</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123741</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307937</v>
+        <v>-0.05296103812307931</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588721</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375526</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577181</v>
+        <v>0.2572294350577182</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379116</v>
+        <v>-0.004000986240379549</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311188</v>
+        <v>0.2383903410311187</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655145</v>
+        <v>0.986609460465513</v>
       </c>
     </row>
     <row r="17">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395307</v>
+        <v>0.1057185310395303</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421757</v>
+        <v>0.2543340222421755</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567304</v>
+        <v>0.6776529122567312</v>
       </c>
     </row>
     <row r="18">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733253</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.263687420331363</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546269</v>
+        <v>0.6013412201546265</v>
       </c>
     </row>
     <row r="19">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223222</v>
+        <v>-0.02557154094223246</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538111</v>
+        <v>0.2527597901538113</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966681</v>
+        <v>0.9194160355966674</v>
       </c>
     </row>
     <row r="20">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376401</v>
+        <v>-0.07344622569376417</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541015</v>
+        <v>0.2674578609541011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222785</v>
+        <v>0.7836169672222777</v>
       </c>
     </row>
     <row r="21">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305063</v>
+        <v>0.206316717030506</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450721</v>
+        <v>0.2442896532450723</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719842</v>
+        <v>0.3983578134719851</v>
       </c>
     </row>
     <row r="22">
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.26967484549659</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.527316719680635</v>
       </c>
     </row>
     <row r="23">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445712</v>
+        <v>0.2870672180445714</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517182</v>
+        <v>0.08105838975171822</v>
       </c>
     </row>
     <row r="24">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923912e-10</v>
+        <v>2.713396260923852e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409676</v>
+        <v>-0.5776106069409674</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1143619392421807</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103902e-07</v>
+        <v>4.401383208104e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441743</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377479</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
         <v>0.1145360411757815</v>
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386414</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400217</v>
       </c>
     </row>
     <row r="28">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975727</v>
+        <v>-0.07514354096975728</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223564</v>
+        <v>0.1613683918223568</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120149</v>
+        <v>0.6414556246120157</v>
       </c>
     </row>
     <row r="29">
@@ -2141,93 +2141,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742091</v>
+        <v>0.09749293462742106</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290164</v>
+        <v>0.1543265796290166</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510007</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.006335499136474496</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006871422968197218</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.356524995766646</v>
+        <v>0.0466896994512992</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002418133412192862</v>
+        <v>-0.005012017390962146</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007135781003458521</v>
+        <v>0.008304876992455041</v>
       </c>
       <c r="D31" t="n">
-        <v>0.734704360341828</v>
+        <v>0.5461741835341615</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2280638724458786</v>
+        <v>-0.002418133412192864</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.007135781003458523</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04668969945129909</v>
+        <v>0.7347043603418278</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.005012017390962165</v>
+        <v>-0.004129656026475439</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00830487699245463</v>
+        <v>0.02222260881033177</v>
       </c>
       <c r="D33" t="n">
-        <v>0.54617418353414</v>
+        <v>0.8525770672961275</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.004129656026475389</v>
+        <v>0.006335499136474509</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02222260881033175</v>
+        <v>0.0068714229681972</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8525770672961291</v>
+        <v>0.3565249957666438</v>
       </c>
     </row>
   </sheetData>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9350702643084896</v>
+        <v>0.9350702643084913</v>
       </c>
       <c r="D2" t="n">
         <v>0.8939763606698742</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04109390363861543</v>
+        <v>0.04109390363861709</v>
       </c>
     </row>
     <row r="3">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9001936888236722</v>
+        <v>0.9001936888236747</v>
       </c>
       <c r="D3" t="n">
         <v>0.8548025202490657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04539116857460657</v>
+        <v>0.04539116857460901</v>
       </c>
     </row>
     <row r="4">
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.872018798394698</v>
+        <v>0.8720187983947002</v>
       </c>
       <c r="D4" t="n">
         <v>0.8250397507431066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04697904765159133</v>
+        <v>0.04697904765159355</v>
       </c>
     </row>
     <row r="5">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8436439126637496</v>
+        <v>0.8436439126637518</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7967552731684119</v>
+        <v>0.7967552731684091</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04688863949533773</v>
+        <v>0.04688863949534272</v>
       </c>
     </row>
   </sheetData>
@@ -2385,34 +2385,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>294.5429333691334</v>
+        <v>294.5429333691335</v>
       </c>
       <c r="B2" t="n">
-        <v>5.090005783082184e-66</v>
+        <v>5.090005783082038e-66</v>
       </c>
       <c r="C2" t="n">
-        <v>216.8995869671256</v>
+        <v>216.8995869671257</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>490.0385614716636</v>
+        <v>490.0385614716635</v>
       </c>
       <c r="B3" t="n">
-        <v>1.397724509693088e-108</v>
+        <v>1.397724509693168e-108</v>
       </c>
       <c r="C3" t="n">
-        <v>358.2851542130627</v>
+        <v>358.2851542130626</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>750.9699416161922</v>
+        <v>750.969941616192</v>
       </c>
       <c r="B4" t="n">
-        <v>2.468888780414373e-165</v>
+        <v>2.468888780414512e-165</v>
       </c>
       <c r="C4" t="n">
         <v>546.8142738096298</v>
@@ -2421,25 +2421,25 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.142274341703333</v>
+        <v>1.142274341703325</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2851722601515733</v>
+        <v>0.2851722601515749</v>
       </c>
       <c r="C5" t="n">
-        <v>1.810094443007935</v>
+        <v>1.810094443007927</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.332870369642652</v>
+        <v>1.33287036964266</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2482952173346543</v>
+        <v>0.2482952173346529</v>
       </c>
       <c r="C6" t="n">
-        <v>2.009871622313524</v>
+        <v>2.009871622313532</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -2457,253 +2457,253 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.566766284228126</v>
+        <v>1.566766284228121</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2106772497604381</v>
+        <v>0.2106772497604389</v>
       </c>
       <c r="C8" t="n">
-        <v>2.246893563503261</v>
+        <v>2.246893563503256</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.574957324834555</v>
+        <v>6.574957324834562</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01034234830004299</v>
+        <v>0.01034234830004294</v>
       </c>
       <c r="C9" t="n">
-        <v>6.595292393273056</v>
+        <v>6.595292393273063</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.7436106862930115</v>
+        <v>0.7436106862930084</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3885066958396542</v>
+        <v>0.3885066958396552</v>
       </c>
       <c r="C10" t="n">
-        <v>1.36398863146308</v>
+        <v>1.363988631463077</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.108437182271647</v>
+        <v>1.108437182271642</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2924219228644685</v>
+        <v>0.2924219228644696</v>
       </c>
       <c r="C11" t="n">
-        <v>1.773876620730235</v>
+        <v>1.77387662073023</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.330365865716019</v>
+        <v>0.3303658657160168</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5654437324694624</v>
+        <v>0.5654437324694639</v>
       </c>
       <c r="C12" t="n">
-        <v>0.822544626686604</v>
+        <v>0.8225446266866003</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2.557369788172969</v>
+        <v>2.557369788172973</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1097810910580799</v>
+        <v>0.1097810910580795</v>
       </c>
       <c r="C13" t="n">
-        <v>3.187298512183339</v>
+        <v>3.187298512183345</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.9003581826524371</v>
+        <v>0.9003581826524326</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3426856873782375</v>
+        <v>0.3426856873782387</v>
       </c>
       <c r="C14" t="n">
-        <v>1.545042157420824</v>
+        <v>1.545042157420818</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.432237332778615</v>
+        <v>1.432237332778611</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2313996514054136</v>
+        <v>0.2313996514054142</v>
       </c>
       <c r="C15" t="n">
-        <v>2.111541403804362</v>
+        <v>2.111541403804358</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.063235339674784</v>
+        <v>2.063235339674773</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1508895055131309</v>
+        <v>0.150889505513132</v>
       </c>
       <c r="C16" t="n">
-        <v>2.728435626137824</v>
+        <v>2.728435626137813</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1958606284066902</v>
+        <v>0.1958606284066892</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6580829806410344</v>
+        <v>0.6580829806410352</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6036585835541346</v>
+        <v>0.6036585835541329</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.617202257648764</v>
+        <v>5.617202257648769</v>
       </c>
       <c r="B18" t="n">
         <v>0.01778501760915551</v>
       </c>
       <c r="C18" t="n">
-        <v>5.813193786944893</v>
+        <v>5.813193786944894</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.417029330831436</v>
+        <v>1.417029330831425</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2338929801225864</v>
+        <v>0.2338929801225883</v>
       </c>
       <c r="C19" t="n">
-        <v>2.096079532445892</v>
+        <v>2.09607953244588</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3.645392438578116</v>
+        <v>3.645392438578105</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05622455201226762</v>
+        <v>0.05622455201226794</v>
       </c>
       <c r="C20" t="n">
-        <v>4.152655928876207</v>
+        <v>4.152655928876199</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.2902145522598145</v>
+        <v>0.2902145522598124</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5900830729575449</v>
+        <v>0.5900830729575461</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7610100209091359</v>
+        <v>0.7610100209091329</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.463998911237537</v>
+        <v>3.463998911237524</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06271846142450672</v>
+        <v>0.06271846142450754</v>
       </c>
       <c r="C22" t="n">
-        <v>3.994966021304705</v>
+        <v>3.994966021304686</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.007612562333023579</v>
+        <v>0.007612562333023134</v>
       </c>
       <c r="B23" t="n">
-        <v>0.930472797363936</v>
+        <v>0.930472797363938</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1039641215850033</v>
+        <v>0.1039641215850002</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.376123154591638</v>
+        <v>3.376123154591652</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06614747908136591</v>
+        <v>0.06614747908136559</v>
       </c>
       <c r="C24" t="n">
-        <v>3.918170014164401</v>
+        <v>3.918170014164408</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.409302944936669</v>
+        <v>0.4093029449366652</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5223235151329922</v>
+        <v>0.5223235151329941</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9369844392298771</v>
+        <v>0.9369844392298718</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.193729552093392</v>
+        <v>1.193729552093386</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2745785502907858</v>
+        <v>0.274578550290787</v>
       </c>
       <c r="C26" t="n">
-        <v>1.864709166408127</v>
+        <v>1.86470916640812</v>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.03913855261814785</v>
+        <v>0.03913855261814755</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8431744274775987</v>
+        <v>0.8431744274775992</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2460969825501764</v>
+        <v>0.2460969825501756</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1260727750054008</v>
+        <v>0.1260727750054018</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7225391866368611</v>
+        <v>0.7225391866368602</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4688522611376015</v>
+        <v>0.4688522611376033</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
@@ -2721,37 +2721,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.7834052395931936</v>
+        <v>0.7834052395931964</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3761017155639738</v>
+        <v>0.3761017155639729</v>
       </c>
       <c r="C30" t="n">
-        <v>1.410805207732774</v>
+        <v>1.410805207732777</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.446774758348324</v>
+        <v>2.446774758348333</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1177666210589458</v>
+        <v>0.1177666210589444</v>
       </c>
       <c r="C31" t="n">
-        <v>3.085997405095313</v>
+        <v>3.08599740509533</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.9507764331417977</v>
+        <v>0.9507764331417961</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3295217416659633</v>
+        <v>0.3295217416659637</v>
       </c>
       <c r="C32" t="n">
-        <v>1.601554438276592</v>
+        <v>1.60155443827659</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
@@ -2769,49 +2769,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.2236537360085907</v>
+        <v>0.2236537360085886</v>
       </c>
       <c r="B34" t="n">
-        <v>0.6362699465437953</v>
+        <v>0.636269946543797</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6522891156774225</v>
+        <v>0.6522891156774188</v>
       </c>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.154672888744988</v>
+        <v>1.154672888744984</v>
       </c>
       <c r="B35" t="n">
-        <v>0.282573082523662</v>
+        <v>0.2825730825236627</v>
       </c>
       <c r="C35" t="n">
-        <v>1.823304051576398</v>
+        <v>1.823304051576395</v>
       </c>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.235439357221134</v>
+        <v>1.235439357221142</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2663518146526994</v>
+        <v>0.2663518146526977</v>
       </c>
       <c r="C36" t="n">
-        <v>1.908594984885495</v>
+        <v>1.908594984885503</v>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7306509873324871</v>
+        <v>0.7306509873324792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3926722595246471</v>
+        <v>0.3926722595246493</v>
       </c>
       <c r="C37" t="n">
-        <v>1.348602413001822</v>
+        <v>1.348602413001814</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2821,13 +2821,13 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.1638558207844853</v>
+        <v>0.1638558207844868</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6856310839467153</v>
+        <v>0.6856310839467139</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5444955775617778</v>
+        <v>0.5444955775617809</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2837,13 +2837,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.3127434814315037</v>
+        <v>0.3127434814314985</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5760015348351384</v>
+        <v>0.5760015348351415</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7958554389557251</v>
+        <v>0.7958554389557173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.4413135992851767</v>
+        <v>0.4413135992851749</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5064891174464761</v>
+        <v>0.506489117446477</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9813968236391706</v>
+        <v>0.981396823639168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
